--- a/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 10/XKBH_AnhTuanBG_191026.xlsx
+++ b/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 10/XKBH_AnhTuanBG_191026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\2. Bảo hành\Xuất nhập kho 2026\Xuất kho\Tháng 10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D270F1-1DC8-434C-94BD-32DD8991942E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0015D149-76A3-496B-A0B6-4E09825847EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
   </si>
   <si>
     <t>ID lỗi: 
-VNET861385071448313, VNET861385071531415, VNET861385071461407, VNET861385071530888</t>
+VNET861385071448313, VNET861385071531415, VNET861385071461407, VNET861385071530888, BH giữ lại gửi qua Aithings xử lý</t>
   </si>
 </sst>
 </file>
@@ -469,6 +469,63 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="4"/>
     </xf>
@@ -483,63 +540,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="5"/>
@@ -972,73 +972,73 @@
     <col min="3" max="3" width="13.42578125" style="1" customWidth="1"/>
     <col min="4" max="5" width="15.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" style="1" customWidth="1"/>
     <col min="9" max="14" width="9.140625" style="1" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="42" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="44"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="35" t="s">
+      <c r="A2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="35" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="37"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="37" t="s">
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="39"/>
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:8" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1104,7 +1104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="2" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" s="2" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
         <v>1</v>
       </c>
@@ -1137,22 +1137,22 @@
       <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:8" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="22" t="s">
+      <c r="B12" s="44"/>
+      <c r="C12" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22" t="s">
+      <c r="D12" s="41"/>
+      <c r="E12" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="24" t="s">
+      <c r="F12" s="41"/>
+      <c r="G12" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="H12" s="24"/>
+      <c r="H12" s="43"/>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45" t="s">
@@ -1213,22 +1213,22 @@
       <c r="H17" s="16"/>
     </row>
     <row r="18" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="22" t="s">
+      <c r="B18" s="40"/>
+      <c r="C18" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23" t="s">
+      <c r="D18" s="41"/>
+      <c r="E18" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="24" t="s">
+      <c r="F18" s="42"/>
+      <c r="G18" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="24"/>
+      <c r="H18" s="43"/>
     </row>
     <row r="19" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="20" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1254,12 +1254,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:F18"/>
@@ -1272,6 +1266,12 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:H13"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
